--- a/data/value_statistical_injury.xlsx
+++ b/data/value_statistical_injury.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9923B6-EB46-4162-9EEC-9CBFFC7E158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBB2B01-01BD-4D4E-BCA2-940718A83F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>category</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>absolute</t>
-  </si>
-  <si>
-    <t>vsl</t>
   </si>
 </sst>
 </file>
@@ -399,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -424,7 +421,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="C2">
-        <v>12900</v>
+        <v>14313.09725685786</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -435,7 +432,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="C3">
-        <v>189200</v>
+        <v>209925.42643391524</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -446,7 +443,7 @@
         <v>0.104</v>
       </c>
       <c r="C4">
-        <v>447200</v>
+        <v>496187.37157107244</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -457,7 +454,7 @@
         <v>0.26300000000000001</v>
       </c>
       <c r="C5">
-        <v>1130900</v>
+        <v>1254781.5261845391</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -468,7 +465,7 @@
         <v>0.59099999999999997</v>
       </c>
       <c r="C6">
-        <v>2541300</v>
+        <v>2819680.1596009983</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,19 +476,17 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>4300000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>4300000</v>
+        <v>4771032.4189526197</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>